--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>90</v>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3053,7 +3053,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>120</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>210</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>215</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>220</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>324</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>334</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>363</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>368</v>
       </c>
@@ -8441,7 +8441,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>381</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>386</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>391</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>396</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>401</v>
       </c>
@@ -9036,7 +9036,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>406</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>411</v>
       </c>
@@ -11969,7 +11969,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>511</v>
       </c>
@@ -12084,7 +12084,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>518</v>
       </c>
@@ -13367,7 +13367,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>590</v>
       </c>
@@ -14299,7 +14299,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>619</v>
       </c>
@@ -14995,7 +14995,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>631</v>
       </c>
@@ -15110,7 +15110,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
         <v>634</v>
       </c>
@@ -15229,12 +15229,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO110">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/main/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -39,13 +39,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>FrPractitionerRoleDocument</t>
+    <t>FRPractitionerRoleDocument</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Fr PractitionerRole Document</t>
+    <t>FR PractitionerRole Document</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
